--- a/Example/Контракт2.xlsx
+++ b/Example/Контракт2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\rtfreport\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA7BE4F-D627-4DF5-80C3-3EAFCCF325A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BA2210-2E4D-4012-8F18-B2944CE5A4B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28764" yWindow="8628" windowWidth="34560" windowHeight="18684" xr2:uid="{C627CA6D-C210-4F06-99AC-A491523DCE6C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25536" xr2:uid="{C627CA6D-C210-4F06-99AC-A491523DCE6C}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -142,7 +142,7 @@
             <family val="2"/>
             <charset val="204"/>
           </rPr>
-          <t>Так как запрос не помещается в коментарий именованного запроса, то расположим его в отдельной ячейке, а в комментарии с помщью функции Cell("E7",1) возьмем его содержимое. Укажем вторым параметром что содержимое нужно удалить после прочтения.
+          <t>Так как запрос не помещается в коментарий именованного запроса, то расположим его в отдельной ячейке, а в комментарии с помщью функции Cell("F12",1) возьмем его содержимое. Укажем вторым параметром что содержимое нужно удалить после прочтения.
 При обработке каждой строки рекордсета строка копируется и данные переносятся. Поэтому форматирование (в том числе условное) сорхраняется как в исходной строке.
 Для рекордсета не обязательно писать вручную запрос, можно использовать сохраненные, для этого просто укажите его имя. Если используются параметры их нужно поместить в контекст. Так же можно использовать готовые запросы с форм для этого укажите имя формы добавив спереди знак "@". Подробнее https://github.com/VASilaev/rtfreport?tab=readme-ov-file#AboutScan</t>
         </r>
@@ -463,48 +463,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -515,6 +490,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -831,7 +818,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5138A2-4D08-4964-A7DE-499EB0E879EC}">
   <sheetPr codeName="Лист1"/>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
@@ -840,51 +827,48 @@
     <col min="5" max="5" width="20.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="6.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+    <row r="1" spans="1:8" ht="6.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="3" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -892,219 +876,226 @@
         <f>"{head.Адрес}"</f>
         <v>{head.Адрес}</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="2" t="s">
+      <c r="C10" s="7"/>
+      <c r="D10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="4" t="s">
+      <c r="C12" s="7"/>
+      <c r="D12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
       <c r="E13">
         <f>SUM(E11:E12)+SUM(B11:B12)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E14" s="15"/>
-    </row>
-    <row r="16" spans="1:10" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E14" s="5"/>
+    </row>
+    <row r="16" spans="1:8" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16" t="s">
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="8"/>
+      <c r="E16" s="7"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17" t="s">
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="20"/>
-      <c r="D27" s="18" t="s">
+      <c r="C27" s="11"/>
+      <c r="D27" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="19"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="G2:H6"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="A9:E9"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="E27:E35"/>
@@ -1113,13 +1104,6 @@
     <mergeCell ref="A18:D24"/>
     <mergeCell ref="A27:A35"/>
     <mergeCell ref="D27:D35"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="G2:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Example/Контракт2.xlsx
+++ b/Example/Контракт2.xlsx
@@ -1,25 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
-  <workbookPr codeName="ЭтаКнига" defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ЭтаКнига"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\rtfreport\Example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Current\rtfreport\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BA2210-2E4D-4012-8F18-B2944CE5A4B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25536" xr2:uid="{C627CA6D-C210-4F06-99AC-A491523DCE6C}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="b.record" comment="Cell(&quot;F12&quot;,1)">Лист1!$A$12:$E$12</definedName>
+    <definedName name="b.record" comment="Cell(&quot;G12&quot;,1)">Лист1!$A$12:$E$12</definedName>
     <definedName name="head.record" comment="&quot;select Номер_контракта, Дата_контракта, Фамилия, Имя, Отчество, Адрес, Телефон, Сумма_контракта, Фото2 as фото from Контракты Left join Клиенты on Клиенты.Код_клиента = Контракты.Код_клиента where Код_контракта = %Forms!Контракты!Код_контракта%&quot;">Лист1!$A$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,12 +28,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Ya</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{74B0C141-83ED-4E2F-A503-47CB69C323A4}">
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -51,7 +50,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{9BE10CD3-0968-47F7-B9F4-8332A3FAFCA2}">
+    <comment ref="A2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -67,7 +66,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{7809B64F-C52F-44B0-9922-3381524012E2}">
+    <comment ref="E2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -85,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{9746D632-F4F8-480D-A877-8B652A7CFDE3}">
+    <comment ref="B4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -100,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{42DF7F22-4C32-4401-B54E-A10FB9D48C33}">
+    <comment ref="E5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -115,7 +114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{7D02DBD1-1C61-47DF-AF1D-3133E12DA00C}">
+    <comment ref="E6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -131,7 +130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{5211FE57-4E84-4B17-AC58-DDF4DA798D64}">
+    <comment ref="E12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -148,7 +147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{6BC05DD5-A1FC-4EDD-9A63-F76403806EC3}">
+    <comment ref="E13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -163,7 +162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0" shapeId="0" xr:uid="{EA945F3F-25BD-4F2C-859B-948C692712EE}">
+    <comment ref="E27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -180,7 +179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E37" authorId="0" shapeId="0" xr:uid="{132AA830-441C-4898-94B8-8CCB9726A3C9}">
+    <comment ref="E37" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -225,14 +224,7 @@
     <t>Сумма</t>
   </si>
   <si>
-    <t>select qMain.n as nL, sum(nPayL) as nSumPayL, qMain.nR as nR, sum(Платеж) as nSumPayR
-from (select n, n + qHalf.nHalf as nR, Платеж as nPayL from ((SELECT d1.id + d2.id*10 + d3.id*100 + 1 as n from digits d1, digits d2, digits d3)d inner join (select round(max(Номер_недели)/2+0.05,0) as nHalf from Платежи where Код_контракта = %Forms!Контракты!Код_контракта%) qHalf on d.n &lt;= qHalf.nHalf) left join  (select Номер_недели, Платеж from  Платежи where Код_контракта = %Forms!Контракты!Код_контракта%) as tPayL on tPayL.Номер_недели = d.n) qMain left join (select Номер_недели, Платеж from  Платежи where Код_контракта = %Forms!Контракты!Код_контракта%) as tPayL on tPayL.Номер_недели = qMain.nR group by n, nr;</t>
-  </si>
-  <si>
     <t>Общая сумма:</t>
-  </si>
-  <si>
-    <t>{b.nL}</t>
   </si>
   <si>
     <t>{b.nSumPayL}</t>
@@ -294,13 +286,31 @@
   </si>
   <si>
     <t>Тест вывода изображения из БД</t>
+  </si>
+  <si>
+    <t>select t.*, d1.id as dd10, d2.id as dd100  
+from
+ ( 
+  select qMain.n as nL, sum(nPayL) as nSumPayL, qMain.nR as nR, sum(Платеж) as nSumPayR
+  from 
+   (select n, n + qHalf.nHalf as nR, Платеж as nPayL 
+    from 
+      ((SELECT d1.id + d2.id*10 + d3.id*100 + 1 as n from digits d1, digits d2, digits d3)d inner join (select round(max(Номер_недели)/2+0.05,0) as nHalf from Платежи where Код_контракта = %Forms!Контракты!Код_контракта%) qHalf on d.n &lt;= qHalf.nHalf) 
+      left join  (select Номер_недели, Платеж from  Платежи where Код_контракта = %Forms!Контракты!Код_контракта%) as tPayL on tPayL.Номер_недели = d.n
+   ) qMain 
+   left join (select Номер_недели, Платеж from  Платежи where Код_контракта = %Forms!Контракты!Код_контракта%) as tPayL on tPayL.Номер_недели = qMain.nR 
+  group by n, nr
+ ) t, digits as d1, digits as d2;</t>
+  </si>
+  <si>
+    <t>{b.nL + b.dd10*10 + b.dd100*100}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,6 +356,15 @@
       <family val="3"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -463,13 +482,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -500,9 +537,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -816,281 +857,304 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5138A2-4D08-4964-A7DE-499EB0E879EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист1"/>
-  <dimension ref="A1:H37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.109375" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="6.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
+    <row r="1" spans="1:9" ht="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:9" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="9"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>13</v>
       </c>
       <c r="B6" t="str">
         <f>"{head.Адрес}"</f>
         <v>{head.Адрес}</v>
       </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="11"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="7"/>
+      <c r="C10" s="15"/>
       <c r="D10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="24"/>
+      <c r="D12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="E12" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="12"/>
+      <c r="G12" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="23" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
       <c r="E13">
         <f>SUM(E11:E12)+SUM(B11:B12)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E14" s="5"/>
-    </row>
-    <row r="16" spans="1:8" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="16" spans="1:9" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="15"/>
+      <c r="F16" s="11"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="8"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="21"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="8"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="8"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="8"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="8"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="8"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="11"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="7"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3"/>
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="7"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="7"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="13"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="G2:H6"/>
+    <mergeCell ref="H2:I6"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B12:C12"/>

--- a/Example/Контракт2.xlsx
+++ b/Example/Контракт2.xlsx
@@ -31,6 +31,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Ya</author>
+    <author>User</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
@@ -130,7 +131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0">
+    <comment ref="E10" authorId="1" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -138,10 +139,9 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
+            <charset val="1"/>
           </rPr>
-          <t>Так как запрос не помещается в коментарий именованного запроса, то расположим его в отдельной ячейке, а в комментарии с помщью функции Cell("F12",1) возьмем его содержимое. Укажем вторым параметром что содержимое нужно удалить после прочтения.
+          <t>Так как запрос не помещается в коментарий именованного запроса, то расположим его в отдельной ячейке, а в комментарии с помщью функции Cell("G12",1) возьмем его содержимое. Укажем вторым параметром что содержимое нужно удалить после прочтения.
 При обработке каждой строки рекордсета строка копируется и данные переносятся. Поэтому форматирование (в том числе условное) сорхраняется как в исходной строке.
 Для рекордсета не обязательно писать вручную запрос, можно использовать сохраненные, для этого просто укажите его имя. Если используются параметры их нужно поместить в контекст. Так же можно использовать готовые запросы с форм для этого укажите имя формы добавив спереди знак "@". Подробнее https://github.com/VASilaev/rtfreport?tab=readme-ov-file#AboutScan</t>
         </r>
@@ -288,7 +288,10 @@
     <t>Тест вывода изображения из БД</t>
   </si>
   <si>
-    <t>select t.*, d1.id as dd10, d2.id as dd100  
+    <t>{b.nL + b.dd10*10 + b.dd100*100}</t>
+  </si>
+  <si>
+    <t>select t.*, d1.id as dd10, d2.id as dd100, d3.id as dd1000 
 from
  ( 
   select qMain.n as nL, sum(nPayL) as nSumPayL, qMain.nR as nR, sum(Платеж) as nSumPayR
@@ -300,10 +303,7 @@
    ) qMain 
    left join (select Номер_недели, Платеж from  Платежи where Код_контракта = %Forms!Контракты!Код_контракта%) as tPayL on tPayL.Номер_недели = qMain.nR 
   group by n, nr
- ) t, digits as d1, digits as d2;</t>
-  </si>
-  <si>
-    <t>{b.nL + b.dd10*10 + b.dd100*100}</t>
+ ) t, digits as d1, digits as d2, digits as d3;</t>
   </si>
 </sst>
 </file>
@@ -507,6 +507,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -543,7 +544,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -870,35 +870,35 @@
   <sheetData>
     <row r="1" spans="1:9" ht="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:9" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
       <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
       <c r="F4" s="9"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -907,8 +907,8 @@
       <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -918,8 +918,8 @@
         <f>"{head.Адрес}"</f>
         <v>{head.Адрес}</v>
       </c>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -930,23 +930,23 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
       <c r="F9" s="11"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="16"/>
       <c r="D10" s="1" t="s">
         <v>1</v>
       </c>
@@ -964,13 +964,13 @@
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="24" t="s">
+      <c r="A12" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="24"/>
+      <c r="C12" s="25"/>
       <c r="D12" s="2" t="s">
         <v>5</v>
       </c>
@@ -979,16 +979,16 @@
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
       <c r="E13">
         <f>SUM(E11:E12)+SUM(B11:B12)</f>
         <v>0</v>
@@ -999,155 +999,155 @@
       <c r="F14" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14" t="s">
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="15"/>
+      <c r="E16" s="16"/>
       <c r="F16" s="11"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21" t="s">
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="8"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="21"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
       <c r="F19" s="8"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="21"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
       <c r="F20" s="8"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="21"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
       <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="21"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
       <c r="F22" s="8"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="21"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
       <c r="F23" s="8"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
       <c r="F24" s="11"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="17" t="s">
+      <c r="C27" s="20"/>
+      <c r="D27" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="18" t="s">
         <v>19</v>
       </c>
       <c r="F27" s="7"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
       <c r="F28" s="7"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
       <c r="F29" s="7"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
       <c r="F30" s="7"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
       <c r="F31" s="7"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
       <c r="F32" s="7"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
       <c r="F33" s="7"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
       <c r="F34" s="7"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
+      <c r="A35" s="19"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
       <c r="F35" s="13"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25"/>
